--- a/analysis/paper tables and figures/figure 6 fuzz driver quality evaluation results.xlsx
+++ b/analysis/paper tables and figures/figure 6 fuzz driver quality evaluation results.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\misc\GitHub\FuzzDojo\analysis\paper tables and figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SW\Desktop\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" tabRatio="500"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="23263" windowHeight="12463" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Quality-chart" sheetId="12" r:id="rId1"/>
@@ -176,11 +176,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -194,17 +197,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -951,11 +951,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="536047712"/>
-        <c:axId val="536048104"/>
+        <c:axId val="663505904"/>
+        <c:axId val="663501984"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="536047712"/>
+        <c:axId val="663505904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -998,7 +998,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536048104"/>
+        <c:crossAx val="663501984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1006,7 +1006,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="536048104"/>
+        <c:axId val="663501984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1124,7 +1124,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536047712"/>
+        <c:crossAx val="663505904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1774,7 +1774,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2059,12 +2059,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="14.15234375" customWidth="1"/>
+    <col min="2" max="2" width="15.07421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -2081,8 +2082,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2098,8 +2099,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="10"/>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2113,8 +2114,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2130,8 +2131,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
@@ -2145,8 +2146,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -2162,8 +2163,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
       <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
@@ -2177,8 +2178,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -2194,8 +2195,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
       <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
@@ -2209,8 +2210,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2226,8 +2227,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
       <c r="B11" s="3" t="s">
         <v>1</v>
       </c>
@@ -2241,8 +2242,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2258,8 +2259,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
@@ -2273,8 +2274,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2290,8 +2291,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
       <c r="B15" s="3" t="s">
         <v>1</v>
       </c>
@@ -2305,8 +2306,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2322,8 +2323,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="12"/>
       <c r="B17" s="3" t="s">
         <v>1</v>
       </c>
@@ -2337,8 +2338,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2354,8 +2355,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
       <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
@@ -2369,8 +2370,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -2386,8 +2387,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
       <c r="B21" s="3" t="s">
         <v>1</v>
       </c>
@@ -2401,161 +2402,161 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15"/>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15"/>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
-      <c r="B31" s="15"/>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15"/>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
-      <c r="B33" s="15"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
-      <c r="B34" s="15"/>
+      <c r="B34" s="8"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="14"/>
-      <c r="B35" s="15"/>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="14"/>
-      <c r="B37" s="15"/>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
-      <c r="B38" s="15"/>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="B38" s="8"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
-      <c r="B39" s="15"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
-      <c r="B40" s="15"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
-      <c r="B41" s="15"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
-      <c r="B42" s="15"/>
+      <c r="B42" s="8"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="14"/>
-      <c r="B43" s="15"/>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
-      <c r="B44" s="15"/>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="15"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2567,6 +2568,16 @@
     <sortCondition ref="A2:A19"/>
   </sortState>
   <mergeCells count="20">
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A41:A42"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A20:A21"/>
@@ -2577,16 +2588,6 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A41:A42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
